--- a/data/samples/ParentSamples.xlsx
+++ b/data/samples/ParentSamples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingyang/dev/trunk/server/testAutomation/data/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054D31F9-DF28-8B4D-9244-1E49BAE5786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB667C03-F20F-D945-A112-23AA73FB20C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="3200" windowWidth="28040" windowHeight="17440" xr2:uid="{2704F8E4-3691-EB47-AEE9-813C8905D274}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>MaterialInputs/Parent_SampleType</t>
-  </si>
-  <si>
     <t>#parent04</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>"parent07, "parent05</t>
+  </si>
+  <si>
+    <t>MaterialInputs/PS +-_.:&amp;()/☃Åä</t>
   </si>
 </sst>
 </file>
@@ -433,37 +433,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/samples/ParentSamples.xlsx
+++ b/data/samples/ParentSamples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingyang/dev/trunk/server/testAutomation/data/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB667C03-F20F-D945-A112-23AA73FB20C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55606C99-B096-CE4A-A3FF-E9E8D046E7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="3200" windowWidth="28040" windowHeight="17440" xr2:uid="{2704F8E4-3691-EB47-AEE9-813C8905D274}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <t>"parent07, "parent05</t>
   </si>
   <si>
-    <t>MaterialInputs/PS +-_.:&amp;()/☃Åä</t>
+    <t>MaterialInputs/PS+- _.:&amp;()/☃Åä</t>
   </si>
 </sst>
 </file>

--- a/data/samples/ParentSamples.xlsx
+++ b/data/samples/ParentSamples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingyang/dev/trunk/server/testAutomation/data/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054D31F9-DF28-8B4D-9244-1E49BAE5786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55606C99-B096-CE4A-A3FF-E9E8D046E7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="3200" windowWidth="28040" windowHeight="17440" xr2:uid="{2704F8E4-3691-EB47-AEE9-813C8905D274}"/>
   </bookViews>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>MaterialInputs/Parent_SampleType</t>
-  </si>
-  <si>
     <t>#parent04</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>"parent07, "parent05</t>
+  </si>
+  <si>
+    <t>MaterialInputs/PS+- _.:&amp;()/☃Åä</t>
   </si>
 </sst>
 </file>
@@ -433,37 +433,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
